--- a/docs/assets/infraestructura/s2-e3-registro-prueba-recuperacion.xlsx
+++ b/docs/assets/infraestructura/s2-e3-registro-prueba-recuperacion.xlsx
@@ -484,7 +484,7 @@
         <v>Nota 1</v>
       </c>
       <c r="B10" t="str">
-        <v>REC-01 a REC-04 se ejecutaron en una base de prueba aislada; los tiempos no representan la base real.</v>
+        <v>REC-01 a REC-04 se ejecutaron en una base de prueba aislada. REC-05 se ejecutó sobre la base real (2026-10-24), que hoy tiene muy pocas filas: su RTO debe volver a medirse cuando la réplica tenga volumen.</v>
       </c>
     </row>
   </sheetData>
@@ -707,16 +707,16 @@
         <v>REC-05</v>
       </c>
       <c r="B6" t="str">
-        <v>Pendiente</v>
+        <v>2026-10-24 16:35 (UTC−5)</v>
       </c>
       <c r="C6" t="str">
         <v>Restauración con la base real del equipo</v>
       </c>
       <c r="D6" t="str">
-        <v>MySQL (PC local)</v>
+        <v>MySQL 8.0.30 (PC local, cermat_db)</v>
       </c>
       <c r="E6" t="str">
-        <v>restore.js hacia cermat_db_verificacion</v>
+        <v>node scripts/backup.js (cuenta cermat_respaldo) y node scripts/restore.js hacia cermat_db_verificacion</v>
       </c>
       <c r="F6" t="str">
         <v>&lt; 1 h</v>
@@ -725,19 +725,19 @@
         <v>≤ 24 h</v>
       </c>
       <c r="H6" t="str">
-        <v>—</v>
+        <v>0,23 s</v>
       </c>
       <c r="I6" t="str">
-        <v>—</v>
+        <v>SHA-256 verificado. Filas: matrículas 1, pagos 1, schema_migraciones 3, resto 0. 9 rutinas, 6 triggers y 3 vistas; objetos completos</v>
       </c>
       <c r="J6" t="str">
-        <v>Pendiente de ejecución</v>
+        <v>Recuperación completa</v>
       </c>
       <c r="K6" t="str">
-        <v>Pendiente</v>
+        <v>Ejecutado</v>
       </c>
       <c r="L6" t="str">
-        <v>A adjuntar: salida de consola y línea del registro</v>
+        <v>registro-restauraciones.jsonl (respaldo cermat_db_2026-10-24T21-35-08.sql); captura de consola por adjuntar</v>
       </c>
     </row>
     <row r="7">

--- a/docs/assets/infraestructura/s2-e3-registro-prueba-recuperacion.xlsx
+++ b/docs/assets/infraestructura/s2-e3-registro-prueba-recuperacion.xlsx
@@ -7,7 +7,7 @@
     <sheet name="Registro" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1">'Registro'!A1:L13</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1">'Registro'!A1:L15</definedName>
   </definedNames>
 </workbook>
 </file>
@@ -484,7 +484,7 @@
         <v>Nota 1</v>
       </c>
       <c r="B10" t="str">
-        <v>REC-01 a REC-04 se ejecutaron en una base de prueba aislada. REC-05 se ejecutó sobre la base real (2026-10-24), que hoy tiene muy pocas filas: su RTO debe volver a medirse cuando la réplica tenga volumen.</v>
+        <v>REC-01 a REC-04 se ejecutaron en una base de prueba aislada y REC-05 sobre la base real (2026-10-24). REC-13 y REC-14 son recuperaciones en otro servidor: de la PC al VPS y del VPS a la PC. La base real tiene muy pocas filas: el RTO debe volver a medirse cuando la réplica tenga volumen.</v>
       </c>
     </row>
   </sheetData>
@@ -496,7 +496,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L13"/>
+  <dimension ref="A1:L15"/>
   <cols>
     <col min="1" max="1" width="8.83203125" customWidth="1"/>
     <col min="2" max="2" width="26.83203125" customWidth="1"/>
@@ -507,7 +507,7 @@
     <col min="7" max="7" width="19.83203125" customWidth="1"/>
     <col min="8" max="8" width="12.83203125" customWidth="1"/>
     <col min="9" max="9" width="60.83203125" customWidth="1"/>
-    <col min="10" max="10" width="25.83203125" customWidth="1"/>
+    <col min="10" max="10" width="60.83203125" customWidth="1"/>
     <col min="11" max="11" width="11.83203125" customWidth="1"/>
     <col min="12" max="12" width="60.83203125" customWidth="1"/>
   </cols>
@@ -1006,10 +1006,86 @@
         <v>A adjuntar: captura y resultado de las pruebas</v>
       </c>
     </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>REC-13</v>
+      </c>
+      <c r="B14" t="str">
+        <v>2026-10-24</v>
+      </c>
+      <c r="C14" t="str">
+        <v>Recuperación en otro servidor: respaldo de la PC restaurado en el VPS</v>
+      </c>
+      <c r="D14" t="str">
+        <v>MySQL 8.0.46 (VPS, cermat_db)</v>
+      </c>
+      <c r="E14" t="str">
+        <v>sha256sum -c del respaldo cermat_db_2026-10-24T21-35-08.sql y restauración con mysql (manual de despliegue §9.3)</v>
+      </c>
+      <c r="F14" t="str">
+        <v>&lt; 1 h</v>
+      </c>
+      <c r="G14" t="str">
+        <v>≤ 24 h</v>
+      </c>
+      <c r="H14" t="str">
+        <v>0,33 s</v>
+      </c>
+      <c r="I14" t="str">
+        <v>Huella SHA-256 correcta. 8 tablas, 9 funciones y procedimientos, 6 triggers, 3 vistas y 1 pago. Hallazgo posterior: la base se creó con utf8mb4_unicode_ci y las rutinas quedaron con otra collation que las tablas (corregido el 2026-10-24 a las 22:06)</v>
+      </c>
+      <c r="J14" t="str">
+        <v>Recuperación completa; defecto de collation detectado después</v>
+      </c>
+      <c r="K14" t="str">
+        <v>Ejecutado</v>
+      </c>
+      <c r="L14" t="str">
+        <v>Manual de despliegue §9.3 y §9.6</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>REC-14</v>
+      </c>
+      <c r="B15" t="str">
+        <v>2026-10-24 22:22 (UTC−5)</v>
+      </c>
+      <c r="C15" t="str">
+        <v>Recuperación en otro servidor: respaldo diario del VPS restaurado en la PC</v>
+      </c>
+      <c r="D15" t="str">
+        <v>MySQL 8.0.30 (PC, cermat_db_verificacion)</v>
+      </c>
+      <c r="E15" t="str">
+        <v>Copia con scp de los 4 respaldos y sha256sum -c; node scripts/restore.js --archivo con el más reciente</v>
+      </c>
+      <c r="F15" t="str">
+        <v>&lt; 1 h</v>
+      </c>
+      <c r="G15" t="str">
+        <v>≤ 24 h</v>
+      </c>
+      <c r="H15" t="str">
+        <v>0,41 s</v>
+      </c>
+      <c r="I15" t="str">
+        <v>SHA-256 verificado. Filas: matrículas 2, pagos 1, ciclos 1, auditoría 2, schema_migraciones 4, resto 0. 9 rutinas, 6 triggers y 3 vistas; collation coherente (utf8mb4_0900_ai_ci); funciones y sp_estado_cuenta sin errores</v>
+      </c>
+      <c r="J15" t="str">
+        <v>Recuperación completa</v>
+      </c>
+      <c r="K15" t="str">
+        <v>Ejecutado</v>
+      </c>
+      <c r="L15" t="str">
+        <v>registro-restauraciones.jsonl (respaldo cermat_db_2026-10-25T03-18-26.sql)</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:L13"/>
+  <autoFilter ref="A1:L15"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L13"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L15"/>
   </ignoredErrors>
 </worksheet>
 </file>